--- a/extenbooks/S605.xlsx
+++ b/extenbooks/S605.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S605.xlsx
+++ b/extenbooks/S605.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–2025</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -958,54 +958,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S605-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S605 — Government Benefits to Workers (B_w)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_2_BenefitAccounts.csv`, column `total_benefits`</t>
+          <t># S605 — Government Benefits to Workers (B_w)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+          <t>**Chapter**: 6 — The Net Social Wage</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1014,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Source Table**: Appendix Ch6 — `Table6_2_BenefitAccounts.csv`, column `total_benefits`</t>
         </is>
       </c>
     </row>
@@ -1021,31 +1022,39 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: calculated</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cash and in-kind transfers to workers: Social Security, Medicare, Medicaid, UI, veterans, other transfers.</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1066,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>Cash and in-kind transfers to workers: Social Security, Medicare, Medicaid, UI, veterans, other transfers.</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1078,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/Table6_2_BenefitAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1090,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>`data/source/book_tables/Table6_2_BenefitAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1102,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1114,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1126,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1952=10.99B; 1989=521.07B</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1138,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S605_benefits_workers.py`. Both endpoints PASS.</t>
+          <t>1952=10.99B; 1989=521.07B</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1150,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S605_benefits_workers.py`. Both endpoints PASS.</t>
         </is>
       </c>
     </row>
@@ -1153,23 +1162,19 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/Table6_2_BenefitAccounts.csv</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S605_benefits_workers.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1182,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S605.csv</t>
+          <t>data/source/book_tables/Table6_2_BenefitAccounts.csv</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1190,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S605_benefits_workers.py</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S605_benefits_workers.py</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1198,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S605.csv</t>
+          <t xml:space="preserve">       └── data/intermediate/S605.csv</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1206,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S605_benefits_workers.py</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S605_benefits_workers.py</t>
         </is>
       </c>
     </row>
@@ -1209,19 +1214,23 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                 └── data/final/S605.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S605_benefits_workers.py</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1242,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1254,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
         </is>
       </c>
     </row>
@@ -1256,6 +1265,18 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1272,12 +1293,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="61" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1300,196 +1321,295 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B_w captures government transfer payments to workers: Social Security (OASDI), Medicare, Medicaid, unemployment insurance (UI), and other transfers × worker share. Worker share for each program is estimated from program eligibility and recipient income data. Social Security and UI are predominantly worker-directed; Medicare/Medicaid allocation uses income-based worker share.</t>
+          <t>Group I - Directly to workers (100%): Labor training and services; Housing and community services; Income support; Social security; Welfare. Exception: Military disability and military retirement (treated as costs of war, excluded).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group I); KB chunk_38 lines 218-224</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Government transfer payments from NIPA Table 2.1 (Personal Income and Its Disposition, transfer payment lines). Program-level detail from NIPA Tables 3.12 and 3.15 (government social benefits). Social Security data cross-referenced with SSA annual statistical supplements.</t>
+          <t>Group I (100% to labor) 1964: Income support, social security, welfare 29.9 -&gt; 29.9; Housing and community services 2.8 -&gt; 2.8; Labor training and services 0.7 -&gt; 0.7 (Direct, billions of $).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BEA NIPA Tables 2.1, 3.12, 3.15; SSA Statistical Supplement</t>
+          <t>ST_1994, Table N.1 Group I expenditures 1964; KB chunk_38 lines 281-284</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>empirical_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Benefit rate (B/EC) rose from approximately 0.11 in 1952 to 0.28 by 1989, a 155% increase — nearly double the rate of tax growth. The acceleration came from Medicare introduction (1966), Medicaid expansion, Social Security benefit increases (1972 automatic COLA), and countercyclical UI spikes during recessions.</t>
+          <t>B1 = Total benefits to labor 1964 = 68.0 (billions of $).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Table N.1 benefits subtotal; KB chunk_38 line 293</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fig 6.4 shows per-worker benefits rising faster than per-worker taxes across the period, but taxes always exceeding benefits in level terms (hence negative NSW). The three positive-NSW years (1975, 1976, 1983) correspond to deep recessions where countercyclical benefits spiked while tax receipts fell.</t>
+          <t>Benefit rate (B1/EC): 1952: 0.11 (11%) -&gt; 1989: 0.29 (29%); Increased 2.6x (workers received more benefits).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Fig 6.4; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Table N.2 (Benefit rate trend 1952-89); KB chunk_38 lines 359-361</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cross_study_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Post-2001, benefits growth accelerated due to Medicare Part D (2006), ACA Medicaid expansion (2014), and COVID emergency transfers (2020). Both AS2 and Moos agree that rising benefits drive NSW positive in the post-2001 era. COVID peak: +$1.8T in transfer payments (2020), pushing NSW to 9.23% of NI.</t>
+          <t>Purpose: Measure net impact of state expenditures and taxes on standard of living of wage/salary earners.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NSW_COMPARISON_REVIEW.md; moos_nsw_reconciled.csv</t>
+          <t>ST_1994, Appendix N (Concept); KB chunk_38 line 208</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>methodological_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Medicaid allocation to workers is debated: Shaikh-Tonak treat it as a worker benefit since eligibility is income-tested. Some argue employer-sponsored health insurance substitutes reduce the net benefit. The AS2 extension maintains the original treatment for consistency.</t>
+          <t>Group II (workers' share = labor income/personal income): Education; Health and hospitals; Recreational and cultural activities; Energy; Natural resources; Transportation (adjusted by gas share of passenger cars); Postal services.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; NSW_COMPARISON_REVIEW.md</t>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group II); KB chunk_38 lines 226-233</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_log_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEC-006 (2026-03-30): The 1996 Personal Responsibility and Work Opportunity Reconciliation Act (welfare reform) restructured federal benefits programs. NIPA Tables 2.1 and 3.1 provide continuous coverage across this transition, though benefits composition changed significantly. S605 shows a structural break around 1996-1997. The discontinuity is documented but not adjusted — splitting pre/post-1996 would overcomplicate for minimal analytical gain. Flagged in V03 continuity checks.</t>
+          <t>Table N.1 (1964) Social Welfare Expenditures - Group I (100% to labor): Income support, social security, welfare 29.9; Housing and community services 2.8; Labor training and services 0.7. Group II (labor share = 0.727): Education 27.6 -&gt; 20.1; Health and hospitals 6.4 -&gt; 4.7; Transportation 13.1 -&gt; 6.7 (+ gas adjustment). B1 = Total benefits to labor = 68.0 (billions of $).</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NickyData/DECISION_LOG.md, DEC-006</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>ST_1994, Table N.1 (full benefits breakdown 1964); KB chunk_38 lines 280-293</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Workers receive 29-30% of EC back as benefits by 1980s.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Significance of Appendix N; KB chunk_38 line 453</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Government benefits to workers sum Social Security, Medicare, Medicaid, UI, and other transfers allocated by worker share. B/EC ratio rose 155% from 0.11 to 0.28 over 1952-1989, with countercyclical spikes during recessions. DEC-006: 1996 welfare reform creates documented structural break handled via NIPA continuous coverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>Benefit rates (B/EC): 0.11 (1952) -&gt; 0.28 (1988).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994 Extended Time Series Page 160; Salvaged SUMMARY_KEY_FINDINGS line 93</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B_w captures government transfer payments to workers: Social Security (OASDI), Medicare, Medicaid, unemployment insurance (UI), and other transfers × worker share. Worker share for each program is estimated from program eligibility and recipient income data. Social Security and UI are predominantly worker-directed; Medicare/Medicaid allocation uses income-based worker share.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Government transfer payments from NIPA Table 2.1 (Personal Income and Its Disposition, transfer payment lines). Program-level detail from NIPA Tables 3.12 and 3.15 (government social benefits). Social Security data cross-referenced with SSA annual statistical supplements.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BEA NIPA Tables 2.1, 3.12, 3.15; SSA Statistical Supplement</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>empirical_finding</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Medicaid worker allocation is debated given employer-sponsored insurance substitution</t>
+          <t>Benefit rate (B/EC) rose from approximately 0.11 in 1952 to 0.28 by 1989, a 155% increase — nearly double the rate of tax growth. The acceleration came from Medicare introduction (1966), Medicaid expansion, Social Security benefit increases (1972 automatic COLA), and countercyclical UI spikes during recessions.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Medicare Part D and ACA expansion create structural breaks in post-2003 data</t>
+          <t>Fig 6.4 shows per-worker benefits rising faster than per-worker taxes across the period, but taxes always exceeding benefits in level terms (hence negative NSW). The three positive-NSW years (1975, 1976, 1983) correspond to deep recessions where countercyclical benefits spiked while tax receipts fell.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST_1994, Fig 6.4; CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_study_comparison</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COVID-era emergency transfers (2020-2021) are extreme outliers requiring separate treatment</t>
+          <t>Post-2001, benefits growth accelerated due to Medicare Part D (2006), ACA Medicaid expansion (2014), and COVID emergency transfers (2020). Both AS2 and Moos agree that rising benefits drive NSW positive in the post-2001 era. COVID peak: +$1.8T in transfer payments (2020), pushing NSW to 9.23% of NI.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NSW_COMPARISON_REVIEW.md; moos_nsw_reconciled.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>methodological_note</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>In-kind benefits (food stamps, housing assistance) may be underrepresented in NIPA transfer data</t>
+          <t>Medicaid allocation to workers is debated: Shaikh-Tonak treat it as a worker benefit since eligibility is income-tested. Some argue employer-sponsored health insurance substitutes reduce the net benefit. The AS2 extension maintains the original treatment for consistency.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; NSW_COMPARISON_REVIEW.md</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>decision_log_note</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1996 welfare reform structural break documented in V03 continuity checks (DEC-006)</t>
+          <t>[internal-decision-record] (2026-03-30): The 1996 Personal Responsibility and Work Opportunity Reconciliation Act (welfare reform) restructured federal benefits programs. NIPA Tables 2.1 and 3.1 provide continuous coverage across this transition, though benefits composition changed significantly. S605 shows a structural break around 1996-1997. The discontinuity is documented but not adjusted — splitting pre/post-1996 would overcomplicate for minimal analytical gain. Flagged in V03 continuity checks.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[internal-decision-log], [internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="18"/>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S604</t>
+          <t>Group I - Directly to workers (100%): Labor training and services; Housing and community services; Income support; Social security; Welfare. Exception: Military disability and military retirement (treated as costs of war, excluded).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group I); KB chunk_38 lines 218-224</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1617,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S606</t>
+          <t>Group I (100% to labor) 1964: Income support, social security, welfare 29.9 -&gt; 29.9; Housing and community services 2.8 -&gt; 2.8; Labor training and services 0.7 -&gt; 0.7 (Direct, billions of $).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 Group I expenditures 1964; KB chunk_38 lines 281-284</t>
         </is>
       </c>
     </row>
@@ -1505,49 +1630,225 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
+          <t>B1 = Total benefits to labor 1964 = 68.0 (billions of $).</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 benefits subtotal; KB chunk_38 line 293</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Benefit rate (B1/EC): 1952: 0.11 (11%) -&gt; 1989: 0.29 (29%); Increased 2.6x (workers received more benefits).</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 (Benefit rate trend 1952-89); KB chunk_38 lines 359-361</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Purpose: Measure net impact of state expenditures and taxes on standard of living of wage/salary earners.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Concept); KB chunk_38 line 208</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Group II (workers' share = labor income/personal income): Education; Health and hospitals; Recreational and cultural activities; Energy; Natural resources; Transportation (adjusted by gas share of passenger cars); Postal services.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group II); KB chunk_38 lines 226-233</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Table N.1 (1964) Social Welfare Expenditures - Group I (100% to labor): Income support, social security, welfare 29.9; Housing and community services 2.8; Labor training and services 0.7. Group II (labor share = 0.727): Education 27.6 -&gt; 20.1; Health and hospitals 6.4 -&gt; 4.7; Transportation 13.1 -&gt; 6.7 (+ gas adjustment). B1 = Total benefits to labor = 68.0 (billions of $).</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 (full benefits breakdown 1964); KB chunk_38 lines 280-293</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Workers receive 29-30% of EC back as benefits by 1980s.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ST_1994, Significance of Appendix N; KB chunk_38 line 453</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Benefit rates (B/EC): 0.11 (1952) -&gt; 0.28 (1988).</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ST_1994 Extended Time Series Page 160; Salvaged SUMMARY_KEY_FINDINGS line 93</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Government benefits to workers sum Social Security, Medicare, Medicaid, UI, and other transfers allocated by worker share. B/EC ratio rose 155% from 0.11 to 0.28 over 1952-1989, with countercyclical spikes during recessions. [internal-decision-record]: 1996 welfare reform creates documented structural break handled via NIPA continuous coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Medicaid worker allocation is debated given employer-sponsored insurance substitution</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Medicare Part D and ACA expansion create structural breaks in post-2003 data</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>COVID-era emergency transfers (2020-2021) are extreme outliers requiring separate treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>In-kind benefits (food stamps, housing assistance) may be underrepresented in NIPA transfer data</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1996 welfare reform structural break documented in V03 continuity checks ([internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>S604</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>S606</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>S607</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Moos_2017</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Moos, Julie. 2017. The Net Social Wage in the United States, 1952-2012. PhD dissertation.</t>
         </is>
@@ -1564,7 +1865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1627,7 +1928,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1949,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1952": 10.994, "1989": 521.07}</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1973,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
